--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3058-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3058-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E67CAA5-846A-46AD-BC83-162AAA415F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6384A441-5C9C-4721-B058-FAD11107D9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{C22E22D2-E059-4159-901C-93A2C5DDF196}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{0CFDA5A6-BDA9-48D4-B840-81CBC786309A}"/>
   </bookViews>
   <sheets>
     <sheet name="3058-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1553,27 +1553,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1824260D-DA38-40A3-8C46-0299202C228F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{466777E4-79F3-4FD1-94E4-7D9DBFDE1A7F}">
   <dimension ref="A1:X35"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="6.25" customWidth="1"/>
-    <col min="15" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1607,7 +1606,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1643,7 +1642,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1695,7 +1694,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1763,7 +1762,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1835,7 +1834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1907,7 +1906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -1979,7 +1978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2051,7 +2050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2123,7 +2122,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2195,7 +2194,7 @@
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2267,7 +2266,7 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2339,7 +2338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2411,7 +2410,7 @@
         <v>5.91</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2483,7 +2482,7 @@
         <v>6.35</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2555,7 +2554,7 @@
         <v>7.63</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2013</v>
       </c>
@@ -2627,7 +2626,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2012</v>
       </c>
@@ -2699,7 +2698,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2011</v>
       </c>
@@ -2771,7 +2770,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2010</v>
       </c>
@@ -2843,7 +2842,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="41">
         <v>2009</v>
       </c>
@@ -2915,7 +2914,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="43"/>
       <c r="B21" s="44"/>
       <c r="C21" s="18" t="s">
@@ -2943,7 +2942,7 @@
       <c r="W21" s="52"/>
       <c r="X21" s="46"/>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="53">
         <v>2008</v>
       </c>
@@ -3015,7 +3014,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="55"/>
       <c r="B23" s="56"/>
       <c r="C23" s="20" t="s">
@@ -3043,7 +3042,7 @@
       <c r="W23" s="62"/>
       <c r="X23" s="58"/>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="41">
         <v>2007</v>
       </c>
@@ -3115,7 +3114,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="43"/>
       <c r="B25" s="44"/>
       <c r="C25" s="18" t="s">
@@ -3143,7 +3142,7 @@
       <c r="W25" s="52"/>
       <c r="X25" s="46"/>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2006</v>
       </c>
@@ -3215,7 +3214,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="39">
         <v>2005</v>
       </c>
@@ -3287,7 +3286,7 @@
         <v>3.63</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2004</v>
       </c>
@@ -3359,7 +3358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2003</v>
       </c>
@@ -3431,7 +3430,7 @@
         <v>7.81</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2002</v>
       </c>
@@ -3503,7 +3502,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="41">
         <v>2001</v>
       </c>
@@ -3575,7 +3574,7 @@
         <v>8.93</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="43"/>
       <c r="B32" s="44"/>
       <c r="C32" s="18" t="s">
@@ -3603,7 +3602,7 @@
       <c r="W32" s="52"/>
       <c r="X32" s="46"/>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2000</v>
       </c>
@@ -3675,7 +3674,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>1999</v>
       </c>
@@ -3747,7 +3746,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37" t="s">
         <v>51</v>
       </c>
